--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/106.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/106.xlsx
@@ -426,13 +426,13 @@
         <v>-15.03742670515985</v>
       </c>
       <c r="E2">
-        <v>-8.620165188586489</v>
+        <v>-8.29044699608801</v>
       </c>
       <c r="F2">
-        <v>-4.204747523650644</v>
+        <v>-4.385503917880719</v>
       </c>
       <c r="G2">
-        <v>-6.096109228138623</v>
+        <v>-6.693328332877606</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.75212220091424</v>
       </c>
       <c r="E3">
-        <v>-9.495265619724739</v>
+        <v>-9.431441307060632</v>
       </c>
       <c r="F3">
-        <v>-4.024176683718797</v>
+        <v>-4.532454638402545</v>
       </c>
       <c r="G3">
-        <v>-5.677129895234001</v>
+        <v>-6.154937622371471</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.51154086406224</v>
       </c>
       <c r="E4">
-        <v>-10.97901107138992</v>
+        <v>-10.95942089283273</v>
       </c>
       <c r="F4">
-        <v>-4.301951468164749</v>
+        <v>-4.491385839306552</v>
       </c>
       <c r="G4">
-        <v>-5.692782154543674</v>
+        <v>-5.378250533403058</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.36236248535954</v>
       </c>
       <c r="E5">
-        <v>-10.72796605782669</v>
+        <v>-10.71416779752532</v>
       </c>
       <c r="F5">
-        <v>-4.017287152029714</v>
+        <v>-4.228826507315221</v>
       </c>
       <c r="G5">
-        <v>-6.27200182318564</v>
+        <v>-6.013984524945922</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.29114345421389</v>
       </c>
       <c r="E6">
-        <v>-10.69229526806827</v>
+        <v>-10.92730042669633</v>
       </c>
       <c r="F6">
-        <v>-4.047505994883839</v>
+        <v>-4.54619145504317</v>
       </c>
       <c r="G6">
-        <v>-5.070535325527802</v>
+        <v>-5.68489974561467</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.30306874727394</v>
       </c>
       <c r="E7">
-        <v>-12.4282223802726</v>
+        <v>-12.95909538819179</v>
       </c>
       <c r="F7">
-        <v>-4.089814859981824</v>
+        <v>-4.036911175802033</v>
       </c>
       <c r="G7">
-        <v>-5.055396200776714</v>
+        <v>-6.314754208279788</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.37806040850904</v>
       </c>
       <c r="E8">
-        <v>-14.17503594399136</v>
+        <v>-13.35031478618845</v>
       </c>
       <c r="F8">
-        <v>-3.588387503719227</v>
+        <v>-4.033248963514257</v>
       </c>
       <c r="G8">
-        <v>-5.510857745524105</v>
+        <v>-6.138295509945555</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.50023968000498</v>
       </c>
       <c r="E9">
-        <v>-14.38379859574497</v>
+        <v>-13.27074496939967</v>
       </c>
       <c r="F9">
-        <v>-4.169714209451447</v>
+        <v>-4.127051631472467</v>
       </c>
       <c r="G9">
-        <v>-5.882645251766417</v>
+        <v>-5.739540299740341</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.63570019979083</v>
       </c>
       <c r="E10">
-        <v>-15.12175419156092</v>
+        <v>-13.98927794019673</v>
       </c>
       <c r="F10">
-        <v>-3.78874058559733</v>
+        <v>-3.815918491715779</v>
       </c>
       <c r="G10">
-        <v>-5.058617361586425</v>
+        <v>-6.301859633404327</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.75532629851236</v>
       </c>
       <c r="E11">
-        <v>-15.27226708215386</v>
+        <v>-15.20733329335787</v>
       </c>
       <c r="F11">
-        <v>-3.330947482277197</v>
+        <v>-3.370430786164233</v>
       </c>
       <c r="G11">
-        <v>-4.846179654331393</v>
+        <v>-5.68934911881945</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.82858657345532</v>
       </c>
       <c r="E12">
-        <v>-16.66355920847844</v>
+        <v>-16.05712861174126</v>
       </c>
       <c r="F12">
-        <v>-3.456192491743468</v>
+        <v>-3.602802753262744</v>
       </c>
       <c r="G12">
-        <v>-5.197229903315709</v>
+        <v>-5.45496249463905</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.8383160513442</v>
       </c>
       <c r="E13">
-        <v>-17.94295727054749</v>
+        <v>-17.05992748142181</v>
       </c>
       <c r="F13">
-        <v>-2.902632661353088</v>
+        <v>-3.161422093294278</v>
       </c>
       <c r="G13">
-        <v>-4.676732691449336</v>
+        <v>-5.890931547251212</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.78172670928695</v>
       </c>
       <c r="E14">
-        <v>-19.28406937639307</v>
+        <v>-16.6516085655722</v>
       </c>
       <c r="F14">
-        <v>-2.976015244464887</v>
+        <v>-2.907859659664752</v>
       </c>
       <c r="G14">
-        <v>-5.432586517339116</v>
+        <v>-5.248844618818487</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.66921011945745</v>
       </c>
       <c r="E15">
-        <v>-19.43255351063058</v>
+        <v>-17.99534265786822</v>
       </c>
       <c r="F15">
-        <v>-2.218697742170898</v>
+        <v>-2.580648736987128</v>
       </c>
       <c r="G15">
-        <v>-4.759724757573326</v>
+        <v>-4.970987221161916</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.52772622189021</v>
       </c>
       <c r="E16">
-        <v>-20.25823470492312</v>
+        <v>-20.00704478019166</v>
       </c>
       <c r="F16">
-        <v>-2.245965111968849</v>
+        <v>-2.307054722823104</v>
       </c>
       <c r="G16">
-        <v>-4.933147685648047</v>
+        <v>-4.908477500289398</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.3833893038206</v>
       </c>
       <c r="E17">
-        <v>-20.27858113863958</v>
+        <v>-20.21433567789277</v>
       </c>
       <c r="F17">
-        <v>-1.704342055852809</v>
+        <v>-2.14270580174028</v>
       </c>
       <c r="G17">
-        <v>-4.514760940394955</v>
+        <v>-5.469432889191205</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.2670026043676</v>
       </c>
       <c r="E18">
-        <v>-21.61833017380886</v>
+        <v>-21.1638751647691</v>
       </c>
       <c r="F18">
-        <v>-1.09645871955424</v>
+        <v>-1.4109566877011</v>
       </c>
       <c r="G18">
-        <v>-4.353626757362008</v>
+        <v>-5.107285691559251</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.19496074293318</v>
       </c>
       <c r="E19">
-        <v>-23.07075669923699</v>
+        <v>-22.01416861529333</v>
       </c>
       <c r="F19">
-        <v>-0.8813060256577214</v>
+        <v>-1.224125875306297</v>
       </c>
       <c r="G19">
-        <v>-4.940126315644831</v>
+        <v>-5.04469651759379</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.18522982741888</v>
       </c>
       <c r="E20">
-        <v>-24.40614934241088</v>
+        <v>-22.99967324273859</v>
       </c>
       <c r="F20">
-        <v>-0.3611534242548418</v>
+        <v>-0.5669936118090881</v>
       </c>
       <c r="G20">
-        <v>-4.968683081466584</v>
+        <v>-4.935382303887055</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.23941307147139</v>
       </c>
       <c r="E21">
-        <v>-24.89227649866029</v>
+        <v>-23.04097745416255</v>
       </c>
       <c r="F21">
-        <v>-0.2871951257980964</v>
+        <v>-0.1059458529633561</v>
       </c>
       <c r="G21">
-        <v>-4.838240966128221</v>
+        <v>-5.411167287700032</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.36798360442877</v>
       </c>
       <c r="E22">
-        <v>-25.23607824532262</v>
+        <v>-23.88771605259076</v>
       </c>
       <c r="F22">
-        <v>0.5436093339004454</v>
+        <v>-0.03448425385864837</v>
       </c>
       <c r="G22">
-        <v>-4.659941604474153</v>
+        <v>-5.934766480736702</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.55821401925226</v>
       </c>
       <c r="E23">
-        <v>-25.51144116430704</v>
+        <v>-24.07750892672623</v>
       </c>
       <c r="F23">
-        <v>0.5538951719410069</v>
+        <v>0.3143255204795702</v>
       </c>
       <c r="G23">
-        <v>-4.796256627599184</v>
+        <v>-5.158920270335264</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.80149713818935</v>
       </c>
       <c r="E24">
-        <v>-26.26943978608094</v>
+        <v>-25.58929921792091</v>
       </c>
       <c r="F24">
-        <v>0.6825861898029241</v>
+        <v>0.6099532791906578</v>
       </c>
       <c r="G24">
-        <v>-5.591310623219473</v>
+        <v>-6.078351461865972</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-15.06810045768582</v>
       </c>
       <c r="E25">
-        <v>-26.84518997141615</v>
+        <v>-25.9582249383778</v>
       </c>
       <c r="F25">
-        <v>0.9156382465391342</v>
+        <v>0.9369123781778311</v>
       </c>
       <c r="G25">
-        <v>-5.302415866734973</v>
+        <v>-6.301323325026964</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.34065797634522</v>
       </c>
       <c r="E26">
-        <v>-26.15051753016551</v>
+        <v>-25.15546235103808</v>
       </c>
       <c r="F26">
-        <v>1.195667847055507</v>
+        <v>0.948968437358175</v>
       </c>
       <c r="G26">
-        <v>-5.291222912266697</v>
+        <v>-6.49662233802519</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.59021705668907</v>
       </c>
       <c r="E27">
-        <v>-26.77374423699713</v>
+        <v>-25.39585186526125</v>
       </c>
       <c r="F27">
-        <v>1.1451854807941</v>
+        <v>1.180937817898926</v>
       </c>
       <c r="G27">
-        <v>-6.234202014218241</v>
+        <v>-5.927582596916483</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.80154441575034</v>
       </c>
       <c r="E28">
-        <v>-26.48990401467036</v>
+        <v>-24.49671429409029</v>
       </c>
       <c r="F28">
-        <v>1.103107730201496</v>
+        <v>0.9512779256771801</v>
       </c>
       <c r="G28">
-        <v>-6.150852409176011</v>
+        <v>-6.459636923260452</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.95128753022524</v>
       </c>
       <c r="E29">
-        <v>-26.72984068149277</v>
+        <v>-25.35587449672154</v>
       </c>
       <c r="F29">
-        <v>1.037650138032279</v>
+        <v>0.9300037940384832</v>
       </c>
       <c r="G29">
-        <v>-5.845719426821385</v>
+        <v>-6.497545980230647</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-16.02873270075518</v>
       </c>
       <c r="E30">
-        <v>-26.55774961225328</v>
+        <v>-25.05634311195819</v>
       </c>
       <c r="F30">
-        <v>1.143470760270305</v>
+        <v>0.7700361081490651</v>
       </c>
       <c r="G30">
-        <v>-6.034413901468764</v>
+        <v>-5.981269713926844</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.02369107055771</v>
       </c>
       <c r="E31">
-        <v>-26.05796910687075</v>
+        <v>-25.00265805259725</v>
       </c>
       <c r="F31">
-        <v>1.332954833456275</v>
+        <v>1.311927555303612</v>
       </c>
       <c r="G31">
-        <v>-6.269704304581386</v>
+        <v>-6.062484017096245</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.93528213766774</v>
       </c>
       <c r="E32">
-        <v>-25.71043136915209</v>
+        <v>-23.25497049339501</v>
       </c>
       <c r="F32">
-        <v>0.7447212003195122</v>
+        <v>0.9778917135943226</v>
       </c>
       <c r="G32">
-        <v>-5.801646134057068</v>
+        <v>-6.521206449199818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.76756618620864</v>
       </c>
       <c r="E33">
-        <v>-25.43801195827266</v>
+        <v>-23.77819943718926</v>
       </c>
       <c r="F33">
-        <v>0.5481661829832455</v>
+        <v>0.6553279320464035</v>
       </c>
       <c r="G33">
-        <v>-5.609008799672417</v>
+        <v>-6.497324173679515</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.52599283136565</v>
       </c>
       <c r="E34">
-        <v>-24.97080023795329</v>
+        <v>-23.84646165438089</v>
       </c>
       <c r="F34">
-        <v>0.5856812859212295</v>
+        <v>0.6161221312393057</v>
       </c>
       <c r="G34">
-        <v>-5.56084367262156</v>
+        <v>-6.195789754326078</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.22451895797542</v>
       </c>
       <c r="E35">
-        <v>-24.26962943650165</v>
+        <v>-23.1217744874074</v>
       </c>
       <c r="F35">
-        <v>0.680615503751664</v>
+        <v>0.5145419217362107</v>
       </c>
       <c r="G35">
-        <v>-5.038711051258788</v>
+        <v>-5.843683441314734</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-14.86927397957957</v>
       </c>
       <c r="E36">
-        <v>-23.6724867399542</v>
+        <v>-23.32892953088828</v>
       </c>
       <c r="F36">
-        <v>0.2546507611492967</v>
+        <v>0.364327433647354</v>
       </c>
       <c r="G36">
-        <v>-4.527304597443253</v>
+        <v>-5.693056929823434</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.47714163575348</v>
       </c>
       <c r="E37">
-        <v>-22.61714398636266</v>
+        <v>-22.570704485414</v>
       </c>
       <c r="F37">
-        <v>0.1022096214817148</v>
+        <v>0.2804610326857236</v>
       </c>
       <c r="G37">
-        <v>-4.149021800852892</v>
+        <v>-6.001391209714535</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.05065657521985</v>
       </c>
       <c r="E38">
-        <v>-23.20815512910372</v>
+        <v>-22.17531889133029</v>
       </c>
       <c r="F38">
-        <v>0.05255645099050968</v>
+        <v>0.02131457439392633</v>
       </c>
       <c r="G38">
-        <v>-4.976317199480143</v>
+        <v>-5.486674210359729</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.60433711279774</v>
       </c>
       <c r="E39">
-        <v>-22.0880053839884</v>
+        <v>-21.55942831239109</v>
       </c>
       <c r="F39">
-        <v>-0.2849742727911909</v>
+        <v>-0.03653694828278554</v>
       </c>
       <c r="G39">
-        <v>-3.442743394413698</v>
+        <v>-4.835953379160585</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.13628604364697</v>
       </c>
       <c r="E40">
-        <v>-20.8365072502806</v>
+        <v>-20.06557530674079</v>
       </c>
       <c r="F40">
-        <v>-0.1277617368834839</v>
+        <v>-0.09933382435421047</v>
       </c>
       <c r="G40">
-        <v>-4.094354762362906</v>
+        <v>-5.2359732177618</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.65806413716367</v>
       </c>
       <c r="E41">
-        <v>-21.25221663571073</v>
+        <v>-20.71570567765199</v>
       </c>
       <c r="F41">
-        <v>-0.4132610473605419</v>
+        <v>-0.268653778221235</v>
       </c>
       <c r="G41">
-        <v>-3.922997614704691</v>
+        <v>-4.950345969724561</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.16699984785342</v>
       </c>
       <c r="E42">
-        <v>-19.91894331837243</v>
+        <v>-20.45047295502274</v>
       </c>
       <c r="F42">
-        <v>-0.9203204735947725</v>
+        <v>-0.6383740309083216</v>
       </c>
       <c r="G42">
-        <v>-3.389357537047411</v>
+        <v>-4.961724314743036</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.67426053348948</v>
       </c>
       <c r="E43">
-        <v>-19.92088603372172</v>
+        <v>-20.04132079995571</v>
       </c>
       <c r="F43">
-        <v>-0.7528312116879349</v>
+        <v>-0.5335383375122246</v>
       </c>
       <c r="G43">
-        <v>-3.254393216502403</v>
+        <v>-4.469764005425181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.1806120594087</v>
       </c>
       <c r="E44">
-        <v>-19.93674474969658</v>
+        <v>-18.5386010421984</v>
       </c>
       <c r="F44">
-        <v>-1.020163596654197</v>
+        <v>-0.8812695774919982</v>
       </c>
       <c r="G44">
-        <v>-2.706726357395231</v>
+        <v>-4.14175846393973</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.69864605152656</v>
       </c>
       <c r="E45">
-        <v>-18.32356192547016</v>
+        <v>-18.4003376737962</v>
       </c>
       <c r="F45">
-        <v>-0.9130954531075552</v>
+        <v>-0.7455598026261608</v>
       </c>
       <c r="G45">
-        <v>-3.097433631394478</v>
+        <v>-3.635897173902475</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.23366113271788</v>
       </c>
       <c r="E46">
-        <v>-18.81976493638663</v>
+        <v>-17.0001153967285</v>
       </c>
       <c r="F46">
-        <v>-0.9831902459976438</v>
+        <v>-0.9574421020164268</v>
       </c>
       <c r="G46">
-        <v>-3.123643220428888</v>
+        <v>-4.170252329396238</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.797417143555069</v>
       </c>
       <c r="E47">
-        <v>-17.83909219070756</v>
+        <v>-17.28199931828395</v>
       </c>
       <c r="F47">
-        <v>-1.183458006033258</v>
+        <v>-0.9773833905040192</v>
       </c>
       <c r="G47">
-        <v>-2.850072979245674</v>
+        <v>-3.606863689523067</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.396599552497806</v>
       </c>
       <c r="E48">
-        <v>-17.02021729284855</v>
+        <v>-16.88203543697849</v>
       </c>
       <c r="F48">
-        <v>-1.316889770541397</v>
+        <v>-1.171559336659446</v>
       </c>
       <c r="G48">
-        <v>-2.476623579142648</v>
+        <v>-3.960165109474088</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.0367628616124</v>
       </c>
       <c r="E49">
-        <v>-16.33089750787497</v>
+        <v>-16.38706869946612</v>
       </c>
       <c r="F49">
-        <v>-1.698914592629667</v>
+        <v>-1.524828212726934</v>
       </c>
       <c r="G49">
-        <v>-3.276501039613656</v>
+        <v>-3.548180959293946</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.719951056719756</v>
       </c>
       <c r="E50">
-        <v>-16.4008126180794</v>
+        <v>-15.58487669985136</v>
       </c>
       <c r="F50">
-        <v>-1.638418092835816</v>
+        <v>-1.655035142935974</v>
       </c>
       <c r="G50">
-        <v>-2.938047416406266</v>
+        <v>-3.084578783065488</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.441276198662257</v>
       </c>
       <c r="E51">
-        <v>-16.90120899592697</v>
+        <v>-14.93479161368024</v>
       </c>
       <c r="F51">
-        <v>-1.6275242331216</v>
+        <v>-1.830273781896001</v>
       </c>
       <c r="G51">
-        <v>-2.808019119260312</v>
+        <v>-4.011726856248237</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.197489585722405</v>
       </c>
       <c r="E52">
-        <v>-15.46033913616642</v>
+        <v>-14.98082355196821</v>
       </c>
       <c r="F52">
-        <v>-1.84759825775815</v>
+        <v>-1.726000549966405</v>
       </c>
       <c r="G52">
-        <v>-2.951362430565215</v>
+        <v>-3.869366776968497</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.977045433635394</v>
       </c>
       <c r="E53">
-        <v>-14.40316687907577</v>
+        <v>-14.91668677459758</v>
       </c>
       <c r="F53">
-        <v>-1.867406179093892</v>
+        <v>-1.863993305394358</v>
       </c>
       <c r="G53">
-        <v>-3.037466409496119</v>
+        <v>-3.643468391550789</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.778554212026645</v>
       </c>
       <c r="E54">
-        <v>-14.24249662128363</v>
+        <v>-14.0792360763591</v>
       </c>
       <c r="F54">
-        <v>-1.983119993223552</v>
+        <v>-1.765135111176862</v>
       </c>
       <c r="G54">
-        <v>-3.224949224476125</v>
+        <v>-3.377383293831867</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.592600760635931</v>
       </c>
       <c r="E55">
-        <v>-13.43834379242355</v>
+        <v>-13.46491234942655</v>
       </c>
       <c r="F55">
-        <v>-1.880736267339742</v>
+        <v>-1.646860813405149</v>
       </c>
       <c r="G55">
-        <v>-2.48828994162304</v>
+        <v>-3.562247467290309</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.420244394603218</v>
       </c>
       <c r="E56">
-        <v>-13.25003625776259</v>
+        <v>-13.35277827604862</v>
       </c>
       <c r="F56">
-        <v>-1.973465371143924</v>
+        <v>-1.912741898681706</v>
       </c>
       <c r="G56">
-        <v>-3.043269795826462</v>
+        <v>-3.512579352564624</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.253440338883725</v>
       </c>
       <c r="E57">
-        <v>-13.43013366904764</v>
+        <v>-13.10017546742676</v>
       </c>
       <c r="F57">
-        <v>-2.039571574989533</v>
+        <v>-2.230993199530651</v>
       </c>
       <c r="G57">
-        <v>-3.356410987840584</v>
+        <v>-3.9077823474062</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.094229052303802</v>
       </c>
       <c r="E58">
-        <v>-12.20297608313107</v>
+        <v>-12.64225617577113</v>
       </c>
       <c r="F58">
-        <v>-2.054234506386487</v>
+        <v>-2.022409459138333</v>
       </c>
       <c r="G58">
-        <v>-3.323994125920041</v>
+        <v>-3.922689733969538</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.936327945839849</v>
       </c>
       <c r="E59">
-        <v>-13.02919616583053</v>
+        <v>-12.5633022314474</v>
       </c>
       <c r="F59">
-        <v>-1.972661854763208</v>
+        <v>-2.053560215320608</v>
       </c>
       <c r="G59">
-        <v>-4.137961268206187</v>
+        <v>-4.13149577276799</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.782793743964944</v>
       </c>
       <c r="E60">
-        <v>-10.89605848451741</v>
+        <v>-11.82423263102556</v>
       </c>
       <c r="F60">
-        <v>-1.968246656506287</v>
+        <v>-1.700083419035017</v>
       </c>
       <c r="G60">
-        <v>-3.197839167055033</v>
+        <v>-3.853595338019409</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.628031904178484</v>
       </c>
       <c r="E61">
-        <v>-12.46743896517902</v>
+        <v>-11.2050634369048</v>
       </c>
       <c r="F61">
-        <v>-2.128024646260464</v>
+        <v>-1.953936609622926</v>
       </c>
       <c r="G61">
-        <v>-4.53585573657119</v>
+        <v>-4.109404502384433</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.473514678338866</v>
       </c>
       <c r="E62">
-        <v>-10.41875732410895</v>
+        <v>-10.57473155435514</v>
       </c>
       <c r="F62">
-        <v>-2.140597606700155</v>
+        <v>-2.201980459615001</v>
       </c>
       <c r="G62">
-        <v>-4.094586500550656</v>
+        <v>-3.860090628367459</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.313326554248773</v>
       </c>
       <c r="E63">
-        <v>-10.71092993860984</v>
+        <v>-11.21521627563</v>
       </c>
       <c r="F63">
-        <v>-2.480378176347859</v>
+        <v>-2.504838209017723</v>
       </c>
       <c r="G63">
-        <v>-4.695907371212796</v>
+        <v>-4.124977308601165</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.148458404262362</v>
       </c>
       <c r="E64">
-        <v>-10.89052468928004</v>
+        <v>-10.71198960152763</v>
       </c>
       <c r="F64">
-        <v>-2.403093154401471</v>
+        <v>-2.232338468192797</v>
       </c>
       <c r="G64">
-        <v>-4.453972703202857</v>
+        <v>-4.191251119751835</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.975306595452694</v>
       </c>
       <c r="E65">
-        <v>-9.834439265951232</v>
+        <v>-10.46853883887527</v>
       </c>
       <c r="F65">
-        <v>-2.070197146238433</v>
+        <v>-2.174932607178792</v>
       </c>
       <c r="G65">
-        <v>-4.540867902517647</v>
+        <v>-5.061146618378428</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.79598831601189</v>
       </c>
       <c r="E66">
-        <v>-10.37454583237207</v>
+        <v>-10.53292921079034</v>
       </c>
       <c r="F66">
-        <v>-2.50048762341822</v>
+        <v>-2.656981136420297</v>
       </c>
       <c r="G66">
-        <v>-4.933991874760562</v>
+        <v>-5.233543277335976</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.610094132130146</v>
       </c>
       <c r="E67">
-        <v>-10.71236546487027</v>
+        <v>-10.01254414867291</v>
       </c>
       <c r="F67">
-        <v>-2.653152422284557</v>
+        <v>-2.651644793611462</v>
       </c>
       <c r="G67">
-        <v>-4.723927828657187</v>
+        <v>-4.956788291343982</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.421143203805285</v>
       </c>
       <c r="E68">
-        <v>-10.28083359125734</v>
+        <v>-9.936932218166836</v>
       </c>
       <c r="F68">
-        <v>-3.038653073994975</v>
+        <v>-2.4194650077504</v>
       </c>
       <c r="G68">
-        <v>-5.220522901730022</v>
+        <v>-5.786606325672159</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.232290244262796</v>
       </c>
       <c r="E69">
-        <v>-9.74977038742982</v>
+        <v>-9.688133327711419</v>
       </c>
       <c r="F69">
-        <v>-2.893915751173428</v>
+        <v>-2.717442016415827</v>
       </c>
       <c r="G69">
-        <v>-4.825915805085514</v>
+        <v>-4.872319721909478</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.047125790847899</v>
       </c>
       <c r="E70">
-        <v>-10.2129155380903</v>
+        <v>-10.35703422338441</v>
       </c>
       <c r="F70">
-        <v>-2.583335132474407</v>
+        <v>-2.566131598253067</v>
       </c>
       <c r="G70">
-        <v>-4.795336295939266</v>
+        <v>-4.906252813687008</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.869531851255407</v>
       </c>
       <c r="E71">
-        <v>-9.585699245657915</v>
+        <v>-9.642803302894638</v>
       </c>
       <c r="F71">
-        <v>-2.950508983765288</v>
+        <v>-2.683359667995044</v>
       </c>
       <c r="G71">
-        <v>-4.704587621616764</v>
+        <v>-5.037952936330294</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.699837714021124</v>
       </c>
       <c r="E72">
-        <v>-9.712152353848102</v>
+        <v>-9.142954870401992</v>
       </c>
       <c r="F72">
-        <v>-3.007625744555716</v>
+        <v>-2.851039454404526</v>
       </c>
       <c r="G72">
-        <v>-4.680274975176356</v>
+        <v>-4.755695823652033</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.540386517930413</v>
       </c>
       <c r="E73">
-        <v>-9.845792150288462</v>
+        <v>-9.76153083442774</v>
       </c>
       <c r="F73">
-        <v>-3.11413805357508</v>
+        <v>-2.904516368827053</v>
       </c>
       <c r="G73">
-        <v>-4.853386711970386</v>
+        <v>-3.774340877809257</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.388860383385397</v>
       </c>
       <c r="E74">
-        <v>-10.39372391979455</v>
+        <v>-9.962925658970864</v>
       </c>
       <c r="F74">
-        <v>-3.086676845804873</v>
+        <v>-3.052131440005925</v>
       </c>
       <c r="G74">
-        <v>-4.145178257481798</v>
+        <v>-4.483363726500507</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.247523300695113</v>
       </c>
       <c r="E75">
-        <v>-10.52337413063415</v>
+        <v>-9.55983713060011</v>
       </c>
       <c r="F75">
-        <v>-3.383378168669989</v>
+        <v>-2.921222054239311</v>
       </c>
       <c r="G75">
-        <v>-3.834182298977123</v>
+        <v>-4.108305401265396</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.113569279351029</v>
       </c>
       <c r="E76">
-        <v>-10.66948987296565</v>
+        <v>-10.61291111871381</v>
       </c>
       <c r="F76">
-        <v>-3.461394639033049</v>
+        <v>-3.068923275628074</v>
       </c>
       <c r="G76">
-        <v>-3.494732201562413</v>
+        <v>-3.432225791235433</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.988309899331475</v>
       </c>
       <c r="E77">
-        <v>-11.20532155992324</v>
+        <v>-10.8553746740325</v>
       </c>
       <c r="F77">
-        <v>-3.464886207635849</v>
+        <v>-3.235724164223186</v>
       </c>
       <c r="G77">
-        <v>-2.361757580566556</v>
+        <v>-3.35256744446949</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.870266019346357</v>
       </c>
       <c r="E78">
-        <v>-11.18889678469742</v>
+        <v>-10.90830800670816</v>
       </c>
       <c r="F78">
-        <v>-3.468318133785647</v>
+        <v>-3.662582715253174</v>
       </c>
       <c r="G78">
-        <v>-3.073700330423442</v>
+        <v>-3.011591185561176</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.762672515599989</v>
       </c>
       <c r="E79">
-        <v>-11.88490965425433</v>
+        <v>-11.68621380021978</v>
       </c>
       <c r="F79">
-        <v>-3.454664153885303</v>
+        <v>-3.409531384311175</v>
       </c>
       <c r="G79">
-        <v>-2.862480903926862</v>
+        <v>-3.35111411497775</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.664479053344978</v>
       </c>
       <c r="E80">
-        <v>-11.78891053376573</v>
+        <v>-12.19137866119743</v>
       </c>
       <c r="F80">
-        <v>-3.809316403515467</v>
+        <v>-3.67008275371812</v>
       </c>
       <c r="G80">
-        <v>-2.618159332583109</v>
+        <v>-2.819400774824326</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.580862189178602</v>
       </c>
       <c r="E81">
-        <v>-13.68443918389639</v>
+        <v>-12.53672914597039</v>
       </c>
       <c r="F81">
-        <v>-3.704615734006026</v>
+        <v>-3.683416155433581</v>
       </c>
       <c r="G81">
-        <v>-1.911556492681067</v>
+        <v>-2.314512785175617</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.513630762134804</v>
       </c>
       <c r="E82">
-        <v>-14.27634243601696</v>
+        <v>-13.79123871489328</v>
       </c>
       <c r="F82">
-        <v>-3.702780071841422</v>
+        <v>-3.563578728372785</v>
       </c>
       <c r="G82">
-        <v>-1.803649260828523</v>
+        <v>-2.515525799774624</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.470681150057844</v>
       </c>
       <c r="E83">
-        <v>-14.04596084935073</v>
+        <v>-14.66212313673039</v>
       </c>
       <c r="F83">
-        <v>-4.130386638636138</v>
+        <v>-3.735632294669048</v>
       </c>
       <c r="G83">
-        <v>-1.994836576266973</v>
+        <v>-1.726814809407578</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.456205486325904</v>
       </c>
       <c r="E84">
-        <v>-16.32492445065886</v>
+        <v>-16.04834337216638</v>
       </c>
       <c r="F84">
-        <v>-4.000504428448996</v>
+        <v>-3.987702838606132</v>
       </c>
       <c r="G84">
-        <v>-0.8743824385006398</v>
+        <v>-1.391453235733867</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.480753581085585</v>
       </c>
       <c r="E85">
-        <v>-15.80187211735091</v>
+        <v>-16.23523802293695</v>
       </c>
       <c r="F85">
-        <v>-4.418453888061875</v>
+        <v>-4.056675193665427</v>
       </c>
       <c r="G85">
-        <v>-1.477401619024426</v>
+        <v>-1.650827857644686</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.549921722051015</v>
       </c>
       <c r="E86">
-        <v>-17.61495536969792</v>
+        <v>-17.57608294881608</v>
       </c>
       <c r="F86">
-        <v>-4.554442822742455</v>
+        <v>-4.303139347020364</v>
       </c>
       <c r="G86">
-        <v>-0.7707557420303731</v>
+        <v>-0.6897500032299465</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.676622328409671</v>
       </c>
       <c r="E87">
-        <v>-18.69335711293652</v>
+        <v>-18.37875949514966</v>
       </c>
       <c r="F87">
-        <v>-4.609815041782588</v>
+        <v>-4.528988749189232</v>
       </c>
       <c r="G87">
-        <v>-0.5880632864456927</v>
+        <v>-0.9365644153647705</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.866331560570619</v>
       </c>
       <c r="E88">
-        <v>-19.2800118636822</v>
+        <v>-20.02045359172837</v>
       </c>
       <c r="F88">
-        <v>-4.699837869281825</v>
+        <v>-4.608437466791733</v>
       </c>
       <c r="G88">
-        <v>-0.8103929037720671</v>
+        <v>-0.8187354785310305</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.132689476757778</v>
       </c>
       <c r="E89">
-        <v>-20.33642786561357</v>
+        <v>-20.87968172146973</v>
       </c>
       <c r="F89">
-        <v>-4.90682286058674</v>
+        <v>-4.591571078103332</v>
       </c>
       <c r="G89">
-        <v>-0.494129867314412</v>
+        <v>-1.111924012579965</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.477121196354005</v>
       </c>
       <c r="E90">
-        <v>-22.80609909280671</v>
+        <v>-22.09989262825853</v>
       </c>
       <c r="F90">
-        <v>-5.048937572211023</v>
+        <v>-4.647450257993978</v>
       </c>
       <c r="G90">
-        <v>-0.8082609124447764</v>
+        <v>-0.9212266578813272</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.910050542747681</v>
       </c>
       <c r="E91">
-        <v>-24.17747499044556</v>
+        <v>-24.60513501878193</v>
       </c>
       <c r="F91">
-        <v>-5.044011271266575</v>
+        <v>-5.132807286642265</v>
       </c>
       <c r="G91">
-        <v>-0.7165488693703467</v>
+        <v>-1.287955650539632</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.424988975273492</v>
       </c>
       <c r="E92">
-        <v>-26.36422980400949</v>
+        <v>-25.57688214219188</v>
       </c>
       <c r="F92">
-        <v>-5.342146498105937</v>
+        <v>-5.469207288919144</v>
       </c>
       <c r="G92">
-        <v>-0.5215643581983523</v>
+        <v>-0.7935025004307055</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.027512759051301</v>
       </c>
       <c r="E93">
-        <v>-28.80464256063908</v>
+        <v>-28.11031881188703</v>
       </c>
       <c r="F93">
-        <v>-5.238104380681722</v>
+        <v>-5.40725700433338</v>
       </c>
       <c r="G93">
-        <v>-1.35137908198099</v>
+        <v>-1.682754758825417</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.703077471084922</v>
       </c>
       <c r="E94">
-        <v>-29.49787494715528</v>
+        <v>-29.75011547785653</v>
       </c>
       <c r="F94">
-        <v>-4.955074433432409</v>
+        <v>-5.377289156802303</v>
       </c>
       <c r="G94">
-        <v>-1.810723896645945</v>
+        <v>-1.946707865217049</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.44794006996139</v>
       </c>
       <c r="E95">
-        <v>-32.36935540881201</v>
+        <v>-32.28307892201788</v>
       </c>
       <c r="F95">
-        <v>-5.347694074602485</v>
+        <v>-5.65041680011855</v>
       </c>
       <c r="G95">
-        <v>-2.967408644794062</v>
+        <v>-3.132906126847768</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.249536073753015</v>
       </c>
       <c r="E96">
-        <v>-33.49124182370927</v>
+        <v>-33.92892336502462</v>
       </c>
       <c r="F96">
-        <v>-5.457494173843559</v>
+        <v>-5.320710834823694</v>
       </c>
       <c r="G96">
-        <v>-3.397825912536867</v>
+        <v>-3.477944425132768</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.088347938877218</v>
       </c>
       <c r="E97">
-        <v>-36.32850513576405</v>
+        <v>-36.31040256091838</v>
       </c>
       <c r="F97">
-        <v>-5.457545532622532</v>
+        <v>-5.812350201854811</v>
       </c>
       <c r="G97">
-        <v>-3.793148087017857</v>
+        <v>-2.959963227876242</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.965989280007909</v>
       </c>
       <c r="E98">
-        <v>-38.78718122806657</v>
+        <v>-38.43068843299774</v>
       </c>
       <c r="F98">
-        <v>-5.714846388340892</v>
+        <v>-5.886209096223221</v>
       </c>
       <c r="G98">
-        <v>-3.824396326363038</v>
+        <v>-4.537342171518323</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.83978280689918</v>
       </c>
       <c r="E99">
-        <v>-41.12440364748337</v>
+        <v>-41.16197866056201</v>
       </c>
       <c r="F99">
-        <v>-5.61193830589111</v>
+        <v>-5.779634659648647</v>
       </c>
       <c r="G99">
-        <v>-4.299208009787468</v>
+        <v>-4.64560363174357</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.74840476874733</v>
       </c>
       <c r="E100">
-        <v>-42.94835750168579</v>
+        <v>-42.85680081419871</v>
       </c>
       <c r="F100">
-        <v>-5.568847461964882</v>
+        <v>-5.5878493818177</v>
       </c>
       <c r="G100">
-        <v>-5.535809327253592</v>
+        <v>-5.803056426456798</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.60590248627924</v>
       </c>
       <c r="E101">
-        <v>-45.51533657835576</v>
+        <v>-45.2475022474091</v>
       </c>
       <c r="F101">
-        <v>-5.697735631268666</v>
+        <v>-5.751100716091816</v>
       </c>
       <c r="G101">
-        <v>-6.190790830561778</v>
+        <v>-6.084144916559697</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.54233498668479</v>
       </c>
       <c r="E102">
-        <v>-47.31544122419679</v>
+        <v>-47.30702731949054</v>
       </c>
       <c r="F102">
-        <v>-5.755570586597322</v>
+        <v>-5.88465259387336</v>
       </c>
       <c r="G102">
-        <v>-6.677431093198025</v>
+        <v>-6.682840524609194</v>
       </c>
     </row>
   </sheetData>
